--- a/fleet_data.xlsx
+++ b/fleet_data.xlsx
@@ -1,11 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30224"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C5D200EF-74B2-47E6-9118-BDF06C15B6C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tewright\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A76A6753-084D-4E0D-980B-013EC52D6EEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2268" yWindow="2268" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,16 +38,16 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
   <si>
-    <t>vehicle</t>
-  </si>
-  <si>
-    <t>status</t>
-  </si>
-  <si>
-    <t>miles this month</t>
-  </si>
-  <si>
-    <t>days used</t>
+    <t>Vehicle</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Miles This Month</t>
+  </si>
+  <si>
+    <t>Days Used</t>
   </si>
   <si>
     <t>1A</t>
@@ -73,7 +78,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -125,19 +130,19 @@
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DBDD7142-6584-4A54-AED1-6AFA742C7AB7}" name="Table1" displayName="Table1" ref="B3:E8" totalsRowShown="0">
   <autoFilter ref="B3:E8" xr:uid="{DBDD7142-6584-4A54-AED1-6AFA742C7AB7}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{BB97BD52-A535-4252-B486-A6F9AFC700B2}" name="vehicle"/>
-    <tableColumn id="2" xr3:uid="{9D2D35A8-70CA-4C14-B770-E185E24B5AB0}" name="status"/>
-    <tableColumn id="3" xr3:uid="{BF187FAE-7190-4555-8F6B-3E0B62223CA2}" name="miles this month"/>
-    <tableColumn id="4" xr3:uid="{1F9FEE08-D3B7-495C-977B-A802696217DB}" name="days used"/>
+    <tableColumn id="1" xr3:uid="{BB97BD52-A535-4252-B486-A6F9AFC700B2}" name="Vehicle"/>
+    <tableColumn id="2" xr3:uid="{9D2D35A8-70CA-4C14-B770-E185E24B5AB0}" name="Status"/>
+    <tableColumn id="3" xr3:uid="{BF187FAE-7190-4555-8F6B-3E0B62223CA2}" name="Miles This Month"/>
+    <tableColumn id="4" xr3:uid="{1F9FEE08-D3B7-495C-977B-A802696217DB}" name="Days Used"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -175,7 +180,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -281,7 +286,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -423,7 +428,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -432,15 +437,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B3:E8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:5">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>0</v>
       </c>
@@ -454,7 +459,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="2:5">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>4</v>
       </c>
@@ -468,7 +473,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="2:5">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>6</v>
       </c>
@@ -482,7 +487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="2:5">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>8</v>
       </c>
@@ -496,7 +501,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="2:5">
+    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>10</v>
       </c>
@@ -510,7 +515,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="2:5">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>11</v>
       </c>

--- a/fleet_data.xlsx
+++ b/fleet_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tewright\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A76A6753-084D-4E0D-980B-013EC52D6EEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C7FB091B-24AA-4A87-BE7B-9A850623FBC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2268" yWindow="2268" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -53,25 +53,25 @@
     <t>1A</t>
   </si>
   <si>
-    <t>active</t>
-  </si>
-  <si>
     <t>2B</t>
   </si>
   <si>
-    <t>down</t>
-  </si>
-  <si>
     <t>3C</t>
   </si>
   <si>
-    <t>maintenance</t>
-  </si>
-  <si>
     <t>4D</t>
   </si>
   <si>
     <t>5E</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>Down</t>
+  </si>
+  <si>
+    <t>Maintenance</t>
   </si>
 </sst>
 </file>
@@ -464,7 +464,7 @@
         <v>4</v>
       </c>
       <c r="C4" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D4">
         <v>3200</v>
@@ -475,10 +475,10 @@
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C5" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -489,10 +489,10 @@
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -503,10 +503,10 @@
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D7">
         <v>1850</v>
@@ -517,10 +517,10 @@
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C8" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D8">
         <v>2241</v>

--- a/fleet_data.xlsx
+++ b/fleet_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tewright\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C7FB091B-24AA-4A87-BE7B-9A850623FBC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{22A87FB0-9852-478D-8FDA-2BEF780C270F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2268" yWindow="2268" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2964" yWindow="2964" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -53,25 +53,25 @@
     <t>1A</t>
   </si>
   <si>
+    <t>active</t>
+  </si>
+  <si>
     <t>2B</t>
   </si>
   <si>
+    <t>down</t>
+  </si>
+  <si>
     <t>3C</t>
   </si>
   <si>
+    <t>maintenance</t>
+  </si>
+  <si>
     <t>4D</t>
   </si>
   <si>
     <t>5E</t>
-  </si>
-  <si>
-    <t>Active</t>
-  </si>
-  <si>
-    <t>Down</t>
-  </si>
-  <si>
-    <t>Maintenance</t>
   </si>
 </sst>
 </file>
@@ -127,8 +127,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DBDD7142-6584-4A54-AED1-6AFA742C7AB7}" name="Table1" displayName="Table1" ref="B3:E8" totalsRowShown="0">
-  <autoFilter ref="B3:E8" xr:uid="{DBDD7142-6584-4A54-AED1-6AFA742C7AB7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{DBDD7142-6584-4A54-AED1-6AFA742C7AB7}" name="Table1" displayName="Table1" ref="A1:D6" totalsRowShown="0">
+  <autoFilter ref="A1:D6" xr:uid="{DBDD7142-6584-4A54-AED1-6AFA742C7AB7}"/>
   <tableColumns count="4">
     <tableColumn id="1" xr3:uid="{BB97BD52-A535-4252-B486-A6F9AFC700B2}" name="Vehicle"/>
     <tableColumn id="2" xr3:uid="{9D2D35A8-70CA-4C14-B770-E185E24B5AB0}" name="Status"/>
@@ -436,7 +436,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B3:E8"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="9.6640625" bestFit="1" customWidth="1"/>
@@ -445,87 +445,87 @@
     <col min="5" max="5" width="12.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <v>3200</v>
+      </c>
+      <c r="D2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
       <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3">
         <v>0</v>
       </c>
-      <c r="C3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" t="s">
-        <v>3</v>
+      <c r="D3">
+        <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
       <c r="B4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" t="s">
         <v>9</v>
       </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
       <c r="D4">
-        <v>3200</v>
-      </c>
-      <c r="E4">
-        <v>25</v>
+        <v>0</v>
       </c>
     </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
       <c r="B5" t="s">
         <v>5</v>
       </c>
-      <c r="C5" t="s">
-        <v>10</v>
+      <c r="C5">
+        <v>1850</v>
       </c>
       <c r="D5">
-        <v>0</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
+        <v>14</v>
       </c>
     </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
       <c r="B6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" t="s">
-        <v>11</v>
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>2241</v>
       </c>
       <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7">
-        <v>1850</v>
-      </c>
-      <c r="E7">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B8" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8">
-        <v>2241</v>
-      </c>
-      <c r="E8">
         <v>16</v>
       </c>
     </row>

--- a/fleet_data.xlsx
+++ b/fleet_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tewright\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{22A87FB0-9852-478D-8FDA-2BEF780C270F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DE481D73-6A05-4324-B3A7-0CAB84425C6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2964" yWindow="2964" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2616" yWindow="2616" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -53,25 +53,25 @@
     <t>1A</t>
   </si>
   <si>
-    <t>active</t>
-  </si>
-  <si>
     <t>2B</t>
   </si>
   <si>
-    <t>down</t>
-  </si>
-  <si>
     <t>3C</t>
   </si>
   <si>
-    <t>maintenance</t>
-  </si>
-  <si>
     <t>4D</t>
   </si>
   <si>
     <t>5E</t>
+  </si>
+  <si>
+    <t>Active</t>
+  </si>
+  <si>
+    <t>Down</t>
+  </si>
+  <si>
+    <t>Maintenance</t>
   </si>
 </sst>
 </file>
@@ -464,7 +464,7 @@
         <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C2">
         <v>3200</v>
@@ -475,10 +475,10 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C3">
         <v>0</v>
@@ -489,10 +489,10 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C4">
         <v>0</v>
@@ -503,10 +503,10 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C5">
         <v>1850</v>
@@ -517,10 +517,10 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C6">
         <v>2241</v>
